--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.4223750666531</v>
+        <v>2.668635948331129</v>
       </c>
       <c r="D2" t="n">
-        <v>16.77194108010384</v>
+        <v>2.725440425516874</v>
       </c>
       <c r="E2" t="n">
-        <v>28.05880297328665</v>
+        <v>4.559555483159081</v>
       </c>
       <c r="F2" t="n">
-        <v>27.64919574740247</v>
+        <v>4.492994308952901</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>92.67544486809507</v>
+        <v>15.05975979106545</v>
       </c>
       <c r="D3" t="n">
-        <v>91.53323352590257</v>
+        <v>14.87415044795917</v>
       </c>
       <c r="E3" t="n">
-        <v>28.05880297328665</v>
+        <v>4.559555483159081</v>
       </c>
       <c r="F3" t="n">
-        <v>27.64919574740247</v>
+        <v>4.492994308952901</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.93535445531482</v>
+        <v>5.676995098988659</v>
       </c>
       <c r="D4" t="n">
-        <v>35.17282406966225</v>
+        <v>5.715583911320116</v>
       </c>
       <c r="E4" t="n">
-        <v>28.05880297328665</v>
+        <v>4.559555483159081</v>
       </c>
       <c r="F4" t="n">
-        <v>27.64919574740247</v>
+        <v>4.492994308952901</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.54577498744737</v>
+        <v>4.963688435460197</v>
       </c>
       <c r="D5" t="n">
-        <v>31.86281671377007</v>
+        <v>5.177707715987636</v>
       </c>
       <c r="E5" t="n">
-        <v>28.05880297328665</v>
+        <v>4.559555483159081</v>
       </c>
       <c r="F5" t="n">
-        <v>27.64919574740247</v>
+        <v>4.492994308952901</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.10585617534863</v>
+        <v>8.304701628494154</v>
       </c>
       <c r="D6" t="n">
-        <v>52.15490168479067</v>
+        <v>8.475171523778483</v>
       </c>
       <c r="E6" t="n">
-        <v>28.05880297328665</v>
+        <v>4.559555483159081</v>
       </c>
       <c r="F6" t="n">
-        <v>27.64919574740247</v>
+        <v>4.492994308952901</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>84.43185325194578</v>
+        <v>13.72017615344119</v>
       </c>
       <c r="D7" t="n">
-        <v>85.08091423834266</v>
+        <v>13.82564856373068</v>
       </c>
       <c r="E7" t="n">
-        <v>28.05880297328665</v>
+        <v>4.559555483159081</v>
       </c>
       <c r="F7" t="n">
-        <v>27.64919574740247</v>
+        <v>4.492994308952901</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
